--- a/dataset_agreed/saved_models/baserun/greyscale_testrun_run_4/epoch_20/per_file_predictions_epoch_20.xlsx
+++ b/dataset_agreed/saved_models/baserun/greyscale_testrun_run_4/epoch_20/per_file_predictions_epoch_20.xlsx
@@ -946,7 +946,7 @@
     <t>0.0002,0.9978,0.2530,0.0000</t>
   </si>
   <si>
-    <t>0.0016,0.9955,0.3163,0.0001</t>
+    <t>0.0016,0.9955,0.3162,0.0001</t>
   </si>
   <si>
     <t>0.0075,0.9925,0.0006,0.0000</t>

--- a/dataset_agreed/saved_models/baserun/greyscale_testrun_run_4/epoch_20/per_file_predictions_epoch_20.xlsx
+++ b/dataset_agreed/saved_models/baserun/greyscale_testrun_run_4/epoch_20/per_file_predictions_epoch_20.xlsx
@@ -823,16 +823,16 @@
     <t>0.0385,0.9630,0.0004,0.0000</t>
   </si>
   <si>
-    <t>0.0533,0.9654,0.0015,0.0000</t>
-  </si>
-  <si>
-    <t>0.0708,0.9531,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.0148,0.9886,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0342,0.9757,0.0002,0.0000</t>
+    <t>0.0532,0.9654,0.0015,0.0000</t>
+  </si>
+  <si>
+    <t>0.0707,0.9531,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0147,0.9886,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0341,0.9757,0.0002,0.0000</t>
   </si>
   <si>
     <t>0.0145,0.9890,0.0001,0.0000</t>
@@ -844,7 +844,7 @@
     <t>0.0259,0.9824,0.0011,0.0000</t>
   </si>
   <si>
-    <t>0.0239,0.9830,0.0002,0.0000</t>
+    <t>0.0238,0.9830,0.0002,0.0000</t>
   </si>
   <si>
     <t>0.0287,0.9784,0.0002,0.0000</t>
@@ -853,7 +853,7 @@
     <t>0.0216,0.9821,0.0002,0.0000</t>
   </si>
   <si>
-    <t>0.0474,0.9739,0.0018,0.0000</t>
+    <t>0.0473,0.9739,0.0018,0.0000</t>
   </si>
   <si>
     <t>0.0108,0.9922,0.0031,0.0000</t>
@@ -862,7 +862,7 @@
     <t>0.0218,0.9839,0.0070,0.0000</t>
   </si>
   <si>
-    <t>0.0034,0.9965,0.0176,0.0000</t>
+    <t>0.0034,0.9965,0.0177,0.0000</t>
   </si>
   <si>
     <t>0.0237,0.9868,0.0008,0.0000</t>
@@ -883,13 +883,13 @@
     <t>0.0002,0.9998,0.0018,0.0000</t>
   </si>
   <si>
-    <t>0.0497,0.9722,0.0016,0.0000</t>
-  </si>
-  <si>
-    <t>0.0051,0.9962,0.0042,0.0000</t>
-  </si>
-  <si>
-    <t>0.0765,0.9437,0.0165,0.0000</t>
+    <t>0.0496,0.9722,0.0016,0.0000</t>
+  </si>
+  <si>
+    <t>0.0051,0.9962,0.0043,0.0000</t>
+  </si>
+  <si>
+    <t>0.0765,0.9438,0.0165,0.0000</t>
   </si>
   <si>
     <t>0.0250,0.9815,0.0080,0.0000</t>
@@ -898,10 +898,10 @@
     <t>0.0323,0.9781,0.0042,0.0000</t>
   </si>
   <si>
-    <t>0.0526,0.9546,0.0245,0.0000</t>
-  </si>
-  <si>
-    <t>0.0289,0.9524,0.1244,0.0002</t>
+    <t>0.0526,0.9547,0.0245,0.0000</t>
+  </si>
+  <si>
+    <t>0.0289,0.9524,0.1246,0.0002</t>
   </si>
   <si>
     <t>0.0045,0.9972,0.0004,0.0000</t>
@@ -910,7 +910,7 @@
     <t>0.0067,0.9941,0.0025,0.0000</t>
   </si>
   <si>
-    <t>0.0177,0.9830,0.0175,0.0000</t>
+    <t>0.0176,0.9830,0.0175,0.0000</t>
   </si>
   <si>
     <t>0.0024,0.9977,0.0021,0.0000</t>
@@ -928,25 +928,25 @@
     <t>0.0005,0.9993,0.0008,0.0000</t>
   </si>
   <si>
-    <t>0.0005,0.9961,0.5576,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.9654,0.8929,0.0001</t>
-  </si>
-  <si>
-    <t>0.0013,0.9969,0.2699,0.0000</t>
-  </si>
-  <si>
-    <t>0.0663,0.9332,0.0347,0.0001</t>
-  </si>
-  <si>
-    <t>0.0012,0.9976,0.1346,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9978,0.2530,0.0000</t>
-  </si>
-  <si>
-    <t>0.0016,0.9955,0.3162,0.0001</t>
+    <t>0.0005,0.9961,0.5578,0.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.9654,0.8930,0.0001</t>
+  </si>
+  <si>
+    <t>0.0013,0.9969,0.2701,0.0000</t>
+  </si>
+  <si>
+    <t>0.0662,0.9333,0.0347,0.0001</t>
+  </si>
+  <si>
+    <t>0.0012,0.9976,0.1348,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9978,0.2531,0.0000</t>
+  </si>
+  <si>
+    <t>0.0015,0.9955,0.3165,0.0001</t>
   </si>
   <si>
     <t>0.0075,0.9925,0.0006,0.0000</t>
@@ -961,22 +961,22 @@
     <t>0.0001,0.9999,0.0041,0.0000</t>
   </si>
   <si>
-    <t>0.0008,0.9882,0.7834,0.0001</t>
-  </si>
-  <si>
-    <t>0.0013,0.9965,0.2875,0.0001</t>
-  </si>
-  <si>
-    <t>0.0094,0.9894,0.0373,0.0000</t>
-  </si>
-  <si>
-    <t>0.0762,0.9493,0.0069,0.0000</t>
-  </si>
-  <si>
-    <t>0.0107,0.9881,0.0387,0.0000</t>
-  </si>
-  <si>
-    <t>0.0121,0.9864,0.0480,0.0000</t>
+    <t>0.0008,0.9882,0.7835,0.0001</t>
+  </si>
+  <si>
+    <t>0.0013,0.9965,0.2877,0.0001</t>
+  </si>
+  <si>
+    <t>0.0094,0.9894,0.0374,0.0000</t>
+  </si>
+  <si>
+    <t>0.0761,0.9493,0.0069,0.0000</t>
+  </si>
+  <si>
+    <t>0.0107,0.9881,0.0388,0.0000</t>
+  </si>
+  <si>
+    <t>0.0121,0.9864,0.0481,0.0000</t>
   </si>
   <si>
     <t>0.0063,0.9949,0.0001,0.0000</t>
@@ -1000,19 +1000,19 @@
     <t>0.0076,0.9936,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.0000,0.9995,0.7272,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9969,0.6936,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.9961,0.5605,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9968,0.8468,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.9634,0.9244,0.0001</t>
+    <t>0.0000,0.9995,0.7274,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9969,0.6938,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.9961,0.5607,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9968,0.8469,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.9633,0.9245,0.0001</t>
   </si>
   <si>
     <t>0.0003,0.9996,0.0006,0.0000</t>
@@ -1030,55 +1030,55 @@
     <t>0.0033,0.9963,0.0050,0.0000</t>
   </si>
   <si>
-    <t>0.0001,0.9986,0.6139,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9989,0.5352,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9997,0.3984,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9987,0.5059,0.0000</t>
-  </si>
-  <si>
-    <t>0.1167,0.9116,0.0032,0.0000</t>
-  </si>
-  <si>
-    <t>0.0359,0.9503,0.0008,0.0001</t>
+    <t>0.0001,0.9986,0.6140,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9989,0.5354,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9997,0.3986,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9987,0.5061,0.0000</t>
+  </si>
+  <si>
+    <t>0.1166,0.9117,0.0033,0.0000</t>
+  </si>
+  <si>
+    <t>0.0358,0.9503,0.0008,0.0001</t>
   </si>
   <si>
     <t>0.0496,0.9510,0.0004,0.0000</t>
   </si>
   <si>
-    <t>0.0989,0.9171,0.0007,0.0000</t>
+    <t>0.0988,0.9172,0.0007,0.0000</t>
   </si>
   <si>
     <t>0.0931,0.9223,0.0016,0.0000</t>
   </si>
   <si>
-    <t>0.0851,0.8905,0.0012,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9994,0.3840,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9967,0.8857,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.9983,0.2848,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9979,0.5800,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9992,0.7982,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9991,0.1909,0.0000</t>
-  </si>
-  <si>
-    <t>0.0396,0.9762,0.0003,0.0000</t>
+    <t>0.0850,0.8905,0.0012,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9994,0.3843,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9967,0.8858,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.9983,0.2850,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9979,0.5803,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9992,0.7984,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.9991,0.1911,0.0000</t>
+  </si>
+  <si>
+    <t>0.0396,0.9763,0.0003,0.0000</t>
   </si>
   <si>
     <t>0.0157,0.9868,0.0002,0.0000</t>
@@ -1090,7 +1090,7 @@
     <t>0.0143,0.9893,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.0035,0.9961,0.0001,0.0000</t>
+    <t>0.0035,0.9962,0.0001,0.0000</t>
   </si>
   <si>
     <t>0.0383,0.9726,0.0202,0.0000</t>
@@ -1099,10 +1099,10 @@
     <t>0.0031,0.9959,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.1128,0.7375,0.2940,0.0008</t>
-  </si>
-  <si>
-    <t>0.0274,0.9802,0.0002,0.0000</t>
+    <t>0.1129,0.7373,0.2941,0.0008</t>
+  </si>
+  <si>
+    <t>0.0274,0.9803,0.0002,0.0000</t>
   </si>
   <si>
     <t>0.0279,0.9852,0.0036,0.0000</t>
@@ -1117,7 +1117,7 @@
     <t>0.0190,0.9841,0.0007,0.0000</t>
   </si>
   <si>
-    <t>0.0558,0.9533,0.0316,0.0001</t>
+    <t>0.0558,0.9533,0.0317,0.0001</t>
   </si>
   <si>
     <t>0.0185,0.9859,0.0002,0.0000</t>
@@ -1132,10 +1132,10 @@
     <t>0.0176,0.9869,0.0056,0.0000</t>
   </si>
   <si>
-    <t>0.0924,0.9571,0.0011,0.0000</t>
-  </si>
-  <si>
-    <t>0.0315,0.9764,0.0132,0.0000</t>
+    <t>0.0923,0.9571,0.0011,0.0000</t>
+  </si>
+  <si>
+    <t>0.0315,0.9765,0.0132,0.0000</t>
   </si>
   <si>
     <t>0.0004,0.9995,0.0001,0.0000</t>
@@ -1159,7 +1159,7 @@
     <t>0.0073,0.9950,0.0008,0.0000</t>
   </si>
   <si>
-    <t>0.0131,0.9882,0.0166,0.0000</t>
+    <t>0.0131,0.9882,0.0167,0.0000</t>
   </si>
   <si>
     <t>0.0052,0.9962,0.0027,0.0000</t>
@@ -1168,7 +1168,7 @@
     <t>0.0123,0.9909,0.0023,0.0000</t>
   </si>
   <si>
-    <t>0.0023,0.9967,0.0499,0.0000</t>
+    <t>0.0023,0.9967,0.0500,0.0000</t>
   </si>
   <si>
     <t>0.0000,1.0000,0.0006,0.0000</t>
@@ -1195,16 +1195,16 @@
     <t>0.0124,0.9849,0.0009,0.0000</t>
   </si>
   <si>
-    <t>0.0191,0.9894,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.0184,0.9863,0.0002,0.0000</t>
+    <t>0.0191,0.9895,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0184,0.9864,0.0002,0.0000</t>
   </si>
   <si>
     <t>0.0094,0.9936,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.0586,0.9544,0.0231,0.0001</t>
+    <t>0.0586,0.9545,0.0231,0.0001</t>
   </si>
   <si>
     <t>0.0119,0.9864,0.0010,0.0000</t>
@@ -1216,16 +1216,16 @@
     <t>0.0136,0.9910,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.0009,0.9976,0.2918,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9985,0.6434,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9854,0.8721,0.0001</t>
-  </si>
-  <si>
-    <t>0.0021,0.9959,0.1419,0.0000</t>
+    <t>0.0009,0.9976,0.2920,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9985,0.6436,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.9854,0.8722,0.0001</t>
+  </si>
+  <si>
+    <t>0.0021,0.9959,0.1421,0.0000</t>
   </si>
   <si>
     <t>0.0354,0.9835,0.0005,0.0000</t>
@@ -1243,19 +1243,19 @@
     <t>0.0970,0.9177,0.0005,0.0000</t>
   </si>
   <si>
-    <t>0.0323,0.9252,0.0020,0.0003</t>
-  </si>
-  <si>
-    <t>0.0212,0.9647,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.2501,0.7993,0.0021,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9988,0.5724,0.0000</t>
-  </si>
-  <si>
-    <t>0.0130,0.9895,0.0001,0.0000</t>
+    <t>0.0322,0.9252,0.0020,0.0003</t>
+  </si>
+  <si>
+    <t>0.0212,0.9648,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.2500,0.7993,0.0021,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9988,0.5726,0.0000</t>
+  </si>
+  <si>
+    <t>0.0129,0.9895,0.0001,0.0000</t>
   </si>
   <si>
     <t>0.0056,0.9943,0.0002,0.0000</t>
@@ -1264,7 +1264,7 @@
     <t>0.0318,0.9818,0.0002,0.0000</t>
   </si>
   <si>
-    <t>0.0078,0.9940,0.0001,0.0000</t>
+    <t>0.0077,0.9940,0.0001,0.0000</t>
   </si>
   <si>
     <t>0.0574,0.9699,0.0009,0.0000</t>
@@ -1273,16 +1273,16 @@
     <t>0.0083,0.0177,0.9873,0.0006</t>
   </si>
   <si>
-    <t>0.1176,0.7563,0.3278,0.0034</t>
+    <t>0.1176,0.7562,0.3279,0.0034</t>
   </si>
   <si>
     <t>0.0000,0.0000,1.0000,0.0000</t>
   </si>
   <si>
-    <t>0.0577,0.9533,0.0043,0.0000</t>
-  </si>
-  <si>
-    <t>0.0328,0.9779,0.0027,0.0000</t>
+    <t>0.0577,0.9534,0.0043,0.0000</t>
+  </si>
+  <si>
+    <t>0.0328,0.9779,0.0028,0.0000</t>
   </si>
   <si>
     <t>0.0114,0.9913,0.0009,0.0000</t>
@@ -1294,7 +1294,7 @@
     <t>0.0068,0.9956,0.0005,0.0000</t>
   </si>
   <si>
-    <t>0.0043,0.9968,0.0004,0.0000</t>
+    <t>0.0042,0.9968,0.0004,0.0000</t>
   </si>
   <si>
     <t>0.0248,0.9859,0.0011,0.0000</t>
@@ -1303,28 +1303,28 @@
     <t>0.0027,0.9977,0.0017,0.0000</t>
   </si>
   <si>
-    <t>0.0483,0.9730,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0532,0.9678,0.0064,0.0000</t>
-  </si>
-  <si>
-    <t>0.0254,0.9843,0.0002,0.0000</t>
+    <t>0.0482,0.9730,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0531,0.9678,0.0064,0.0000</t>
+  </si>
+  <si>
+    <t>0.0253,0.9843,0.0002,0.0000</t>
   </si>
   <si>
     <t>0.0223,0.9847,0.0003,0.0000</t>
   </si>
   <si>
-    <t>0.0229,0.9880,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0295,0.9832,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0453,0.9696,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0328,0.9770,0.0002,0.0000</t>
+    <t>0.0228,0.9880,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0294,0.9832,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0452,0.9696,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0328,0.9771,0.0002,0.0000</t>
   </si>
   <si>
     <t>0.0005,0.9995,0.0002,0.0000</t>
@@ -1357,22 +1357,22 @@
     <t>0.0095,0.9928,0.0003,0.0000</t>
   </si>
   <si>
-    <t>0.0121,0.9789,0.1441,0.0002</t>
-  </si>
-  <si>
-    <t>0.0030,0.9950,0.1455,0.0001</t>
+    <t>0.0121,0.9789,0.1443,0.0002</t>
+  </si>
+  <si>
+    <t>0.0030,0.9950,0.1456,0.0001</t>
   </si>
   <si>
     <t>0.0066,0.9927,0.0036,0.0000</t>
   </si>
   <si>
-    <t>0.0024,0.9950,0.1943,0.0001</t>
+    <t>0.0023,0.9950,0.1945,0.0001</t>
   </si>
   <si>
     <t>0.0157,0.9827,0.0348,0.0001</t>
   </si>
   <si>
-    <t>0.0583,0.9471,0.0288,0.0001</t>
+    <t>0.0582,0.9471,0.0289,0.0001</t>
   </si>
   <si>
     <t>0.0254,0.9768,0.0203,0.0000</t>
@@ -1393,7 +1393,7 @@
     <t>0.0062,0.9956,0.0021,0.0000</t>
   </si>
   <si>
-    <t>0.0136,0.9861,0.0203,0.0000</t>
+    <t>0.0136,0.9862,0.0204,0.0000</t>
   </si>
   <si>
     <t>0.0063,0.9947,0.0026,0.0000</t>
@@ -1405,13 +1405,13 @@
     <t>0.0099,0.9936,0.0137,0.0000</t>
   </si>
   <si>
-    <t>0.0072,0.9951,0.0001,0.0000</t>
+    <t>0.0071,0.9951,0.0001,0.0000</t>
   </si>
   <si>
     <t>0.0141,0.9923,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.0024,0.9973,0.0001,0.0000</t>
+    <t>0.0023,0.9973,0.0001,0.0000</t>
   </si>
   <si>
     <t>0.0027,0.9970,0.0001,0.0000</t>
@@ -1426,7 +1426,7 @@
     <t>0.0125,0.9905,0.0039,0.0000</t>
   </si>
   <si>
-    <t>0.0097,0.9902,0.0244,0.0000</t>
+    <t>0.0097,0.9902,0.0245,0.0000</t>
   </si>
   <si>
     <t>0.0406,0.9761,0.0019,0.0000</t>
@@ -1435,16 +1435,16 @@
     <t>0.0116,0.9869,0.0169,0.0000</t>
   </si>
   <si>
-    <t>0.0203,0.9702,0.1050,0.0002</t>
-  </si>
-  <si>
-    <t>0.0165,0.9747,0.1153,0.0002</t>
-  </si>
-  <si>
-    <t>0.0010,0.9912,0.6536,0.0001</t>
-  </si>
-  <si>
-    <t>0.0036,0.9863,0.3715,0.0002</t>
+    <t>0.0203,0.9702,0.1051,0.0002</t>
+  </si>
+  <si>
+    <t>0.0165,0.9747,0.1154,0.0002</t>
+  </si>
+  <si>
+    <t>0.0010,0.9912,0.6540,0.0001</t>
+  </si>
+  <si>
+    <t>0.0036,0.9863,0.3718,0.0002</t>
   </si>
   <si>
     <t>0.0095,0.9894,0.0002,0.0000</t>
@@ -1459,13 +1459,13 @@
     <t>0.0175,0.9893,0.0019,0.0000</t>
   </si>
   <si>
-    <t>0.0124,0.9903,0.0001,0.0000</t>
+    <t>0.0124,0.9904,0.0001,0.0000</t>
   </si>
   <si>
     <t>0.0123,0.9898,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.0186,0.9844,0.0003,0.0000</t>
+    <t>0.0186,0.9844,0.0004,0.0000</t>
   </si>
   <si>
     <t>0.0100,0.9910,0.0003,0.0000</t>
@@ -1477,28 +1477,28 @@
     <t>0.0040,0.9960,0.0005,0.0000</t>
   </si>
   <si>
-    <t>0.0048,0.9960,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.9897,0.7150,0.0001</t>
-  </si>
-  <si>
-    <t>0.0041,0.9847,0.3814,0.0002</t>
+    <t>0.0047,0.9960,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.9897,0.7153,0.0001</t>
+  </si>
+  <si>
+    <t>0.0041,0.9847,0.3818,0.0002</t>
   </si>
   <si>
     <t>0.0146,0.9859,0.0272,0.0000</t>
   </si>
   <si>
-    <t>0.0005,0.9807,0.8997,0.0001</t>
-  </si>
-  <si>
-    <t>0.0066,0.9932,0.0269,0.0000</t>
+    <t>0.0005,0.9807,0.8998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0066,0.9932,0.0270,0.0000</t>
   </si>
   <si>
     <t>0.0003,0.9677,0.9672,0.0001</t>
   </si>
   <si>
-    <t>0.0033,0.9913,0.2580,0.0001</t>
+    <t>0.0033,0.9913,0.2583,0.0001</t>
   </si>
   <si>
     <t>0.0030,0.9968,0.0099,0.0000</t>
@@ -1507,10 +1507,10 @@
     <t>0.0522,0.9599,0.0083,0.0000</t>
   </si>
   <si>
-    <t>0.1554,0.9054,0.0034,0.0000</t>
-  </si>
-  <si>
-    <t>0.0881,0.9563,0.0009,0.0000</t>
+    <t>0.1552,0.9054,0.0034,0.0000</t>
+  </si>
+  <si>
+    <t>0.0880,0.9563,0.0009,0.0000</t>
   </si>
   <si>
     <t>0.0036,0.9949,0.0001,0.0000</t>
@@ -1522,7 +1522,7 @@
     <t>0.0254,0.9827,0.0002,0.0000</t>
   </si>
   <si>
-    <t>0.0085,0.9923,0.0002,0.0000</t>
+    <t>0.0085,0.9924,0.0002,0.0000</t>
   </si>
   <si>
     <t>0.0021,0.9969,0.0001,0.0000</t>
@@ -1537,28 +1537,28 @@
     <t>0.0032,0.9955,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.0040,0.9950,0.0407,0.0000</t>
-  </si>
-  <si>
-    <t>0.0023,0.9951,0.1591,0.0000</t>
-  </si>
-  <si>
-    <t>0.0040,0.9909,0.1785,0.0001</t>
+    <t>0.0040,0.9950,0.0408,0.0000</t>
+  </si>
+  <si>
+    <t>0.0023,0.9951,0.1593,0.0000</t>
+  </si>
+  <si>
+    <t>0.0040,0.9909,0.1787,0.0001</t>
   </si>
   <si>
     <t>0.0126,0.9874,0.0253,0.0000</t>
   </si>
   <si>
-    <t>0.0111,0.9837,0.0822,0.0000</t>
+    <t>0.0111,0.9837,0.0823,0.0000</t>
   </si>
   <si>
     <t>0.0672,0.9376,0.0124,0.0001</t>
   </si>
   <si>
-    <t>0.0280,0.9723,0.0184,0.0001</t>
-  </si>
-  <si>
-    <t>0.0009,0.9823,0.7961,0.0001</t>
+    <t>0.0280,0.9723,0.0185,0.0001</t>
+  </si>
+  <si>
+    <t>0.0009,0.9823,0.7962,0.0001</t>
   </si>
   <si>
     <t>0.0661,0.9588,0.0025,0.0000</t>
@@ -1567,16 +1567,16 @@
     <t>0.0137,0.9851,0.0004,0.0000</t>
   </si>
   <si>
-    <t>0.1014,0.9143,0.0017,0.0000</t>
-  </si>
-  <si>
-    <t>0.1567,0.8141,0.0573,0.0013</t>
+    <t>0.1012,0.9144,0.0017,0.0000</t>
+  </si>
+  <si>
+    <t>0.1566,0.8142,0.0574,0.0013</t>
   </si>
   <si>
     <t>0.0938,0.8864,0.0035,0.0002</t>
   </si>
   <si>
-    <t>0.0093,0.9944,0.0019,0.0000</t>
+    <t>0.0092,0.9944,0.0019,0.0000</t>
   </si>
 </sst>
 </file>
